--- a/output/rubella_latex.xlsx
+++ b/output/rubella_latex.xlsx
@@ -453,16 +453,16 @@
         <v>0.2278</v>
       </c>
       <c r="C2" t="n">
-        <v>166</v>
+        <v>72</v>
       </c>
       <c r="D2" t="n">
-        <v>4869</v>
+        <v>2398</v>
       </c>
       <c r="E2" t="n">
-        <v>648</v>
+        <v>317</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -473,16 +473,16 @@
         <v>0.181</v>
       </c>
       <c r="C3" t="n">
-        <v>211</v>
+        <v>57</v>
       </c>
       <c r="D3" t="n">
-        <v>4018</v>
+        <v>1605</v>
       </c>
       <c r="E3" t="n">
-        <v>729</v>
+        <v>228</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -493,16 +493,16 @@
         <v>0.1315</v>
       </c>
       <c r="C4" t="n">
-        <v>332</v>
+        <v>69</v>
       </c>
       <c r="D4" t="n">
-        <v>4526</v>
+        <v>2425</v>
       </c>
       <c r="E4" t="n">
-        <v>959</v>
+        <v>286</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -513,16 +513,16 @@
         <v>0.07815999999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>641</v>
+        <v>55</v>
       </c>
       <c r="D5" t="n">
-        <v>6976</v>
+        <v>1023</v>
       </c>
       <c r="E5" t="n">
-        <v>1745</v>
+        <v>200</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -530,16 +530,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>0.03709</v>
+        <v>0.01772</v>
       </c>
       <c r="C6" t="n">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="D6" t="n">
-        <v>993</v>
+        <v>2036</v>
       </c>
       <c r="E6" t="n">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -550,16 +550,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.03155</v>
+        <v>0.01328</v>
       </c>
       <c r="C7" t="n">
-        <v>185</v>
+        <v>55</v>
       </c>
       <c r="D7" t="n">
-        <v>1283</v>
+        <v>1262</v>
       </c>
       <c r="E7" t="n">
-        <v>452</v>
+        <v>198</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -570,19 +570,19 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>0.02869</v>
+        <v>0.01045</v>
       </c>
       <c r="C8" t="n">
-        <v>282</v>
+        <v>63</v>
       </c>
       <c r="D8" t="n">
-        <v>1981</v>
+        <v>1957</v>
       </c>
       <c r="E8" t="n">
-        <v>812</v>
+        <v>271</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -590,19 +590,19 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.02564</v>
+        <v>0.008004000000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>288</v>
+        <v>74</v>
       </c>
       <c r="D9" t="n">
-        <v>1998</v>
+        <v>1386</v>
       </c>
       <c r="E9" t="n">
-        <v>949</v>
+        <v>253</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -610,19 +610,19 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.02561</v>
+        <v>0.005642</v>
       </c>
       <c r="C10" t="n">
-        <v>1157</v>
+        <v>36</v>
       </c>
       <c r="D10" t="n">
-        <v>7213</v>
+        <v>2019</v>
       </c>
       <c r="E10" t="n">
-        <v>2371</v>
+        <v>146</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -633,16 +633,16 @@
         <v>0.00455</v>
       </c>
       <c r="C11" t="n">
-        <v>1479</v>
+        <v>70</v>
       </c>
       <c r="D11" t="n">
-        <v>11905</v>
+        <v>1100</v>
       </c>
       <c r="E11" t="n">
-        <v>3242</v>
+        <v>226</v>
       </c>
       <c r="F11" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -650,19 +650,19 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.01469</v>
+        <v>0.003801</v>
       </c>
       <c r="C12" t="n">
-        <v>1374</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
-        <v>9167</v>
+        <v>1452</v>
       </c>
       <c r="E12" t="n">
-        <v>2897</v>
+        <v>237</v>
       </c>
       <c r="F12" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
